--- a/metrics/Spinoff5fret_metrics_09022026-1549.xlsx
+++ b/metrics/Spinoff5fret_metrics_09022026-1549.xlsx
@@ -41907,7 +41907,7 @@
         <v>54.16</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>5</v>
@@ -41993,7 +41993,7 @@
         <v>43.53</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3" s="4" t="n">
         <v>4</v>
@@ -42079,7 +42079,7 @@
         <v>39.21</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>4</v>
@@ -42165,7 +42165,7 @@
         <v>37.43</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M5" s="4" t="n">
         <v>4</v>
@@ -42251,7 +42251,7 @@
         <v>37.19</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>4</v>
@@ -42337,7 +42337,7 @@
         <v>37.15</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M7" s="4" t="n">
         <v>4</v>
@@ -42423,7 +42423,7 @@
         <v>35.09</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>4</v>
@@ -42509,7 +42509,7 @@
         <v>34.69</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M9" s="4" t="n">
         <v>4</v>
@@ -42595,7 +42595,7 @@
         <v>33.06</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M10" s="4" t="n">
         <v>4</v>
@@ -42681,7 +42681,7 @@
         <v>32.95</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>4</v>
@@ -42767,7 +42767,7 @@
         <v>32.04</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M12" s="4" t="n">
         <v>4</v>
@@ -42853,7 +42853,7 @@
         <v>31.78</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M13" s="4" t="n">
         <v>4</v>
@@ -42939,7 +42939,7 @@
         <v>31.25</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M14" s="4" t="n">
         <v>4</v>
@@ -43025,7 +43025,7 @@
         <v>30.58</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M15" s="4" t="n">
         <v>4</v>
@@ -43111,7 +43111,7 @@
         <v>30.49</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M16" s="4" t="n">
         <v>4</v>
@@ -43197,7 +43197,7 @@
         <v>30.27</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M17" s="4" t="n">
         <v>4</v>
@@ -43283,7 +43283,7 @@
         <v>30.14</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M18" s="4" t="n">
         <v>4</v>
@@ -43369,7 +43369,7 @@
         <v>29.89</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M19" s="4" t="n">
         <v>4</v>
@@ -43455,7 +43455,7 @@
         <v>29.51</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M20" s="4" t="n">
         <v>4</v>
@@ -43541,7 +43541,7 @@
         <v>28.79</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M21" s="4" t="n">
         <v>4</v>
@@ -43627,7 +43627,7 @@
         <v>28.56</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M22" s="4" t="n">
         <v>4</v>
@@ -43713,7 +43713,7 @@
         <v>28.44</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M23" s="4" t="n">
         <v>3</v>
@@ -43799,7 +43799,7 @@
         <v>28.25</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M24" s="4" t="n">
         <v>3</v>
@@ -43885,7 +43885,7 @@
         <v>28.03</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M25" s="4" t="n">
         <v>3</v>
@@ -43971,7 +43971,7 @@
         <v>27.95</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M26" s="4" t="n">
         <v>3</v>
@@ -44057,7 +44057,7 @@
         <v>27.93</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M27" s="4" t="n">
         <v>3</v>
@@ -44143,7 +44143,7 @@
         <v>27.92</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M28" s="4" t="n">
         <v>3</v>
@@ -44229,7 +44229,7 @@
         <v>27.66</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M29" s="4" t="n">
         <v>3</v>
@@ -44315,7 +44315,7 @@
         <v>27.35</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M30" s="4" t="n">
         <v>3</v>
@@ -44401,7 +44401,7 @@
         <v>27.15</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M31" s="4" t="n">
         <v>3</v>
@@ -44487,7 +44487,7 @@
         <v>26.74</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M32" s="4" t="n">
         <v>3</v>
@@ -44573,7 +44573,7 @@
         <v>26.5</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M33" s="4" t="n">
         <v>3</v>
@@ -44659,7 +44659,7 @@
         <v>25.82</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M34" s="4" t="n">
         <v>3</v>
@@ -44745,7 +44745,7 @@
         <v>25.74</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M35" s="4" t="n">
         <v>3</v>
@@ -44831,7 +44831,7 @@
         <v>25.4</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M36" s="4" t="n">
         <v>3</v>
@@ -44917,7 +44917,7 @@
         <v>24.89</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M37" s="4" t="n">
         <v>3</v>
@@ -45003,7 +45003,7 @@
         <v>24.87</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M38" s="4" t="n">
         <v>3</v>
@@ -45089,7 +45089,7 @@
         <v>24.84</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M39" s="4" t="n">
         <v>3</v>
@@ -45175,7 +45175,7 @@
         <v>24.83</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M40" s="4" t="n">
         <v>3</v>
@@ -45261,7 +45261,7 @@
         <v>24.17</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M41" s="4" t="n">
         <v>3</v>
@@ -45347,7 +45347,7 @@
         <v>23.56</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M42" s="4" t="n">
         <v>3</v>
@@ -45433,7 +45433,7 @@
         <v>23.45</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M43" s="4" t="n">
         <v>3</v>
@@ -45519,7 +45519,7 @@
         <v>23.02</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M44" s="4" t="n">
         <v>3</v>
@@ -45605,7 +45605,7 @@
         <v>23</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M45" s="4" t="n">
         <v>3</v>
@@ -45691,7 +45691,7 @@
         <v>22.84</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M46" s="4" t="n">
         <v>3</v>
@@ -45777,7 +45777,7 @@
         <v>22.82</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M47" s="4" t="n">
         <v>3</v>
@@ -45863,7 +45863,7 @@
         <v>22.82</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M48" s="4" t="n">
         <v>3</v>
@@ -45949,7 +45949,7 @@
         <v>22.52</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M49" s="4" t="n">
         <v>3</v>
@@ -46035,7 +46035,7 @@
         <v>22.52</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M50" s="4" t="n">
         <v>3</v>
@@ -46121,7 +46121,7 @@
         <v>22.41</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M51" s="4" t="n">
         <v>3</v>
@@ -46207,7 +46207,7 @@
         <v>22.36</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M52" s="4" t="n">
         <v>3</v>
@@ -46293,7 +46293,7 @@
         <v>22.32</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M53" s="4" t="n">
         <v>3</v>
@@ -46379,7 +46379,7 @@
         <v>22.24</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M54" s="4" t="n">
         <v>3</v>
@@ -46465,7 +46465,7 @@
         <v>22.15</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M55" s="4" t="n">
         <v>3</v>
@@ -46551,7 +46551,7 @@
         <v>22.07</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M56" s="4" t="n">
         <v>3</v>
@@ -46637,7 +46637,7 @@
         <v>22.06</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M57" s="4" t="n">
         <v>3</v>
@@ -46723,7 +46723,7 @@
         <v>21.6</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M58" s="4" t="n">
         <v>3</v>
@@ -46809,7 +46809,7 @@
         <v>21.46</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M59" s="4" t="n">
         <v>3</v>
@@ -46895,7 +46895,7 @@
         <v>21.19</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M60" s="4" t="n">
         <v>3</v>
@@ -46981,7 +46981,7 @@
         <v>21.18</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M61" s="4" t="n">
         <v>3</v>
@@ -47067,7 +47067,7 @@
         <v>20.73</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M62" s="4" t="n">
         <v>3</v>
@@ -47153,7 +47153,7 @@
         <v>20.72</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M63" s="4" t="n">
         <v>3</v>
@@ -47239,7 +47239,7 @@
         <v>20.67</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M64" s="4" t="n">
         <v>3</v>
@@ -47325,7 +47325,7 @@
         <v>20.66</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M65" s="4" t="n">
         <v>3</v>
@@ -47411,7 +47411,7 @@
         <v>20.63</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M66" s="4" t="n">
         <v>3</v>
@@ -47497,7 +47497,7 @@
         <v>20.6</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M67" s="4" t="n">
         <v>3</v>
@@ -47583,7 +47583,7 @@
         <v>20.56</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M68" s="4" t="n">
         <v>3</v>
@@ -47669,7 +47669,7 @@
         <v>20.54</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M69" s="4" t="n">
         <v>3</v>
@@ -47755,7 +47755,7 @@
         <v>20.41</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M70" s="4" t="n">
         <v>3</v>
@@ -47841,7 +47841,7 @@
         <v>20.26</v>
       </c>
       <c r="L71" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M71" s="4" t="n">
         <v>3</v>
@@ -47927,7 +47927,7 @@
         <v>20.19</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M72" s="4" t="n">
         <v>3</v>
@@ -48013,7 +48013,7 @@
         <v>20.18</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M73" s="4" t="n">
         <v>3</v>
@@ -48099,7 +48099,7 @@
         <v>19.97</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M74" s="4" t="n">
         <v>3</v>
@@ -48185,7 +48185,7 @@
         <v>19.92</v>
       </c>
       <c r="L75" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M75" s="4" t="n">
         <v>3</v>
@@ -48271,7 +48271,7 @@
         <v>19.53</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M76" s="4" t="n">
         <v>3</v>
@@ -48357,7 +48357,7 @@
         <v>19.51</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M77" s="4" t="n">
         <v>3</v>
@@ -48443,7 +48443,7 @@
         <v>19.42</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M78" s="4" t="n">
         <v>3</v>
@@ -48529,7 +48529,7 @@
         <v>19.31</v>
       </c>
       <c r="L79" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M79" s="4" t="n">
         <v>3</v>
@@ -48615,7 +48615,7 @@
         <v>19.26</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M80" s="4" t="n">
         <v>3</v>
@@ -48701,7 +48701,7 @@
         <v>19.12</v>
       </c>
       <c r="L81" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M81" s="4" t="n">
         <v>3</v>
@@ -48787,7 +48787,7 @@
         <v>19</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M82" s="4" t="n">
         <v>3</v>
@@ -48873,7 +48873,7 @@
         <v>18.96</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M83" s="4" t="n">
         <v>3</v>
@@ -48959,7 +48959,7 @@
         <v>18.85</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M84" s="4" t="n">
         <v>3</v>
@@ -49045,7 +49045,7 @@
         <v>18.76</v>
       </c>
       <c r="L85" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M85" s="4" t="n">
         <v>3</v>
@@ -49131,7 +49131,7 @@
         <v>18.49</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M86" s="4" t="n">
         <v>3</v>
@@ -49217,7 +49217,7 @@
         <v>18.44</v>
       </c>
       <c r="L87" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M87" s="4" t="n">
         <v>3</v>
@@ -49303,7 +49303,7 @@
         <v>18.4</v>
       </c>
       <c r="L88" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M88" s="4" t="n">
         <v>3</v>
@@ -49389,7 +49389,7 @@
         <v>18.28</v>
       </c>
       <c r="L89" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M89" s="4" t="n">
         <v>2</v>
@@ -49475,7 +49475,7 @@
         <v>18.12</v>
       </c>
       <c r="L90" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M90" s="4" t="n">
         <v>2</v>
@@ -49561,7 +49561,7 @@
         <v>18.08</v>
       </c>
       <c r="L91" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M91" s="4" t="n">
         <v>2</v>
@@ -49647,7 +49647,7 @@
         <v>18.06</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M92" s="4" t="n">
         <v>2</v>
@@ -49733,7 +49733,7 @@
         <v>18.04</v>
       </c>
       <c r="L93" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M93" s="4" t="n">
         <v>2</v>
@@ -49819,7 +49819,7 @@
         <v>17.92</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M94" s="4" t="n">
         <v>2</v>
@@ -49905,7 +49905,7 @@
         <v>17.86</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M95" s="4" t="n">
         <v>2</v>
@@ -49991,7 +49991,7 @@
         <v>17.84</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M96" s="4" t="n">
         <v>2</v>
@@ -50077,7 +50077,7 @@
         <v>17.75</v>
       </c>
       <c r="L97" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M97" s="4" t="n">
         <v>2</v>
@@ -50163,7 +50163,7 @@
         <v>17.72</v>
       </c>
       <c r="L98" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M98" s="4" t="n">
         <v>2</v>
@@ -50249,7 +50249,7 @@
         <v>17.71</v>
       </c>
       <c r="L99" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M99" s="4" t="n">
         <v>2</v>
@@ -50335,7 +50335,7 @@
         <v>17.66</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M100" s="4" t="n">
         <v>2</v>
@@ -50421,7 +50421,7 @@
         <v>17.55</v>
       </c>
       <c r="L101" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M101" s="4" t="n">
         <v>2</v>
@@ -50507,7 +50507,7 @@
         <v>17.46</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M102" s="4" t="n">
         <v>2</v>
@@ -50593,7 +50593,7 @@
         <v>17.22</v>
       </c>
       <c r="L103" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M103" s="4" t="n">
         <v>2</v>
@@ -50679,7 +50679,7 @@
         <v>17.14</v>
       </c>
       <c r="L104" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M104" s="4" t="n">
         <v>2</v>
@@ -50765,7 +50765,7 @@
         <v>17.13</v>
       </c>
       <c r="L105" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M105" s="4" t="n">
         <v>2</v>
@@ -50851,7 +50851,7 @@
         <v>17.11</v>
       </c>
       <c r="L106" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M106" s="4" t="n">
         <v>2</v>
@@ -50937,7 +50937,7 @@
         <v>17.02</v>
       </c>
       <c r="L107" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M107" s="4" t="n">
         <v>2</v>
@@ -51023,7 +51023,7 @@
         <v>16.95</v>
       </c>
       <c r="L108" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M108" s="4" t="n">
         <v>2</v>
@@ -51109,7 +51109,7 @@
         <v>16.94</v>
       </c>
       <c r="L109" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M109" s="4" t="n">
         <v>2</v>
@@ -51195,7 +51195,7 @@
         <v>16.92</v>
       </c>
       <c r="L110" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M110" s="4" t="n">
         <v>2</v>
@@ -51281,7 +51281,7 @@
         <v>16.9</v>
       </c>
       <c r="L111" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M111" s="4" t="n">
         <v>2</v>
@@ -51367,7 +51367,7 @@
         <v>16.88</v>
       </c>
       <c r="L112" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M112" s="4" t="n">
         <v>2</v>
@@ -51453,7 +51453,7 @@
         <v>16.62</v>
       </c>
       <c r="L113" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M113" s="4" t="n">
         <v>2</v>
@@ -51539,7 +51539,7 @@
         <v>16.46</v>
       </c>
       <c r="L114" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M114" s="4" t="n">
         <v>2</v>
@@ -51625,7 +51625,7 @@
         <v>16.43</v>
       </c>
       <c r="L115" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M115" s="4" t="n">
         <v>2</v>
@@ -51711,7 +51711,7 @@
         <v>16.38</v>
       </c>
       <c r="L116" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M116" s="4" t="n">
         <v>2</v>
@@ -51797,7 +51797,7 @@
         <v>16.34</v>
       </c>
       <c r="L117" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M117" s="4" t="n">
         <v>2</v>
@@ -51883,7 +51883,7 @@
         <v>16.32</v>
       </c>
       <c r="L118" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M118" s="4" t="n">
         <v>2</v>
@@ -51969,7 +51969,7 @@
         <v>16.24</v>
       </c>
       <c r="L119" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M119" s="4" t="n">
         <v>2</v>
@@ -52055,7 +52055,7 @@
         <v>16.22</v>
       </c>
       <c r="L120" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M120" s="4" t="n">
         <v>2</v>
@@ -52141,7 +52141,7 @@
         <v>16.17</v>
       </c>
       <c r="L121" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M121" s="4" t="n">
         <v>2</v>
@@ -52227,7 +52227,7 @@
         <v>16.11</v>
       </c>
       <c r="L122" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M122" s="4" t="n">
         <v>2</v>
@@ -52313,7 +52313,7 @@
         <v>16.05</v>
       </c>
       <c r="L123" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M123" s="4" t="n">
         <v>2</v>
@@ -52399,7 +52399,7 @@
         <v>16.02</v>
       </c>
       <c r="L124" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M124" s="4" t="n">
         <v>2</v>
@@ -52485,7 +52485,7 @@
         <v>15.99</v>
       </c>
       <c r="L125" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M125" s="4" t="n">
         <v>2</v>
@@ -52571,7 +52571,7 @@
         <v>15.97</v>
       </c>
       <c r="L126" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M126" s="4" t="n">
         <v>2</v>
@@ -52657,7 +52657,7 @@
         <v>15.92</v>
       </c>
       <c r="L127" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M127" s="4" t="n">
         <v>2</v>
@@ -52743,7 +52743,7 @@
         <v>15.88</v>
       </c>
       <c r="L128" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M128" s="4" t="n">
         <v>2</v>
@@ -52829,7 +52829,7 @@
         <v>15.83</v>
       </c>
       <c r="L129" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M129" s="4" t="n">
         <v>2</v>
@@ -52915,7 +52915,7 @@
         <v>15.79</v>
       </c>
       <c r="L130" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M130" s="4" t="n">
         <v>2</v>
@@ -53001,7 +53001,7 @@
         <v>15.69</v>
       </c>
       <c r="L131" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M131" s="4" t="n">
         <v>2</v>
@@ -53087,7 +53087,7 @@
         <v>15.61</v>
       </c>
       <c r="L132" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M132" s="4" t="n">
         <v>2</v>
@@ -53173,7 +53173,7 @@
         <v>15.43</v>
       </c>
       <c r="L133" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M133" s="4" t="n">
         <v>2</v>
@@ -53259,7 +53259,7 @@
         <v>15.41</v>
       </c>
       <c r="L134" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M134" s="4" t="n">
         <v>2</v>
@@ -53345,7 +53345,7 @@
         <v>15.39</v>
       </c>
       <c r="L135" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M135" s="4" t="n">
         <v>2</v>
@@ -53431,7 +53431,7 @@
         <v>15.34</v>
       </c>
       <c r="L136" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M136" s="4" t="n">
         <v>2</v>
@@ -53517,7 +53517,7 @@
         <v>15.27</v>
       </c>
       <c r="L137" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M137" s="4" t="n">
         <v>2</v>
@@ -53603,7 +53603,7 @@
         <v>15.21</v>
       </c>
       <c r="L138" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M138" s="4" t="n">
         <v>2</v>
@@ -53689,7 +53689,7 @@
         <v>15.12</v>
       </c>
       <c r="L139" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M139" s="4" t="n">
         <v>2</v>
@@ -53775,7 +53775,7 @@
         <v>15.11</v>
       </c>
       <c r="L140" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M140" s="4" t="n">
         <v>2</v>
@@ -53861,7 +53861,7 @@
         <v>15.1</v>
       </c>
       <c r="L141" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M141" s="4" t="n">
         <v>2</v>
@@ -53947,7 +53947,7 @@
         <v>15.02</v>
       </c>
       <c r="L142" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M142" s="4" t="n">
         <v>2</v>
@@ -54033,7 +54033,7 @@
         <v>15</v>
       </c>
       <c r="L143" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M143" s="4" t="n">
         <v>2</v>
@@ -54119,7 +54119,7 @@
         <v>14.97</v>
       </c>
       <c r="L144" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M144" s="4" t="n">
         <v>2</v>
@@ -54205,7 +54205,7 @@
         <v>14.96</v>
       </c>
       <c r="L145" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M145" s="4" t="n">
         <v>2</v>
@@ -54291,7 +54291,7 @@
         <v>14.94</v>
       </c>
       <c r="L146" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M146" s="4" t="n">
         <v>2</v>
@@ -54377,7 +54377,7 @@
         <v>14.9</v>
       </c>
       <c r="L147" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M147" s="4" t="n">
         <v>2</v>
@@ -54463,7 +54463,7 @@
         <v>14.88</v>
       </c>
       <c r="L148" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M148" s="4" t="n">
         <v>2</v>
@@ -54549,7 +54549,7 @@
         <v>14.86</v>
       </c>
       <c r="L149" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M149" s="4" t="n">
         <v>2</v>
@@ -54635,7 +54635,7 @@
         <v>14.74</v>
       </c>
       <c r="L150" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M150" s="4" t="n">
         <v>2</v>
@@ -54721,7 +54721,7 @@
         <v>14.72</v>
       </c>
       <c r="L151" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M151" s="4" t="n">
         <v>2</v>
@@ -54807,7 +54807,7 @@
         <v>14.6</v>
       </c>
       <c r="L152" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M152" s="4" t="n">
         <v>2</v>
@@ -54893,7 +54893,7 @@
         <v>14.54</v>
       </c>
       <c r="L153" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M153" s="4" t="n">
         <v>2</v>
@@ -54979,7 +54979,7 @@
         <v>14.45</v>
       </c>
       <c r="L154" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M154" s="4" t="n">
         <v>2</v>
@@ -55065,7 +55065,7 @@
         <v>14.44</v>
       </c>
       <c r="L155" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M155" s="4" t="n">
         <v>2</v>
@@ -55151,7 +55151,7 @@
         <v>14.34</v>
       </c>
       <c r="L156" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M156" s="4" t="n">
         <v>2</v>
@@ -55237,7 +55237,7 @@
         <v>14.32</v>
       </c>
       <c r="L157" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M157" s="4" t="n">
         <v>2</v>
@@ -55323,7 +55323,7 @@
         <v>14.3</v>
       </c>
       <c r="L158" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M158" s="4" t="n">
         <v>2</v>
@@ -55409,7 +55409,7 @@
         <v>14.19</v>
       </c>
       <c r="L159" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M159" s="4" t="n">
         <v>2</v>
@@ -55495,7 +55495,7 @@
         <v>14.17</v>
       </c>
       <c r="L160" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M160" s="4" t="n">
         <v>2</v>
@@ -55581,7 +55581,7 @@
         <v>14.15</v>
       </c>
       <c r="L161" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M161" s="4" t="n">
         <v>2</v>
@@ -55667,7 +55667,7 @@
         <v>14.14</v>
       </c>
       <c r="L162" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M162" s="4" t="n">
         <v>2</v>
@@ -55753,7 +55753,7 @@
         <v>13.88</v>
       </c>
       <c r="L163" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M163" s="4" t="n">
         <v>2</v>
@@ -55839,7 +55839,7 @@
         <v>13.78</v>
       </c>
       <c r="L164" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M164" s="4" t="n">
         <v>2</v>
@@ -55925,7 +55925,7 @@
         <v>13.71</v>
       </c>
       <c r="L165" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M165" s="4" t="n">
         <v>2</v>
@@ -56011,7 +56011,7 @@
         <v>13.7</v>
       </c>
       <c r="L166" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M166" s="4" t="n">
         <v>2</v>
@@ -56097,7 +56097,7 @@
         <v>13.66</v>
       </c>
       <c r="L167" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M167" s="4" t="n">
         <v>2</v>
@@ -56183,7 +56183,7 @@
         <v>13.64</v>
       </c>
       <c r="L168" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M168" s="4" t="n">
         <v>2</v>
@@ -56269,7 +56269,7 @@
         <v>13.61</v>
       </c>
       <c r="L169" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M169" s="4" t="n">
         <v>2</v>
@@ -56355,7 +56355,7 @@
         <v>13.6</v>
       </c>
       <c r="L170" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M170" s="4" t="n">
         <v>2</v>
@@ -56441,7 +56441,7 @@
         <v>13.56</v>
       </c>
       <c r="L171" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M171" s="4" t="n">
         <v>2</v>
@@ -56527,7 +56527,7 @@
         <v>13.47</v>
       </c>
       <c r="L172" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M172" s="4" t="n">
         <v>2</v>
@@ -56613,7 +56613,7 @@
         <v>13.45</v>
       </c>
       <c r="L173" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M173" s="4" t="n">
         <v>2</v>
@@ -56699,7 +56699,7 @@
         <v>13.38</v>
       </c>
       <c r="L174" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M174" s="4" t="n">
         <v>2</v>
@@ -56785,7 +56785,7 @@
         <v>13.38</v>
       </c>
       <c r="L175" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M175" s="4" t="n">
         <v>2</v>
@@ -56871,7 +56871,7 @@
         <v>13.38</v>
       </c>
       <c r="L176" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M176" s="4" t="n">
         <v>2</v>
@@ -56957,7 +56957,7 @@
         <v>13.32</v>
       </c>
       <c r="L177" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M177" s="4" t="n">
         <v>2</v>
@@ -57043,7 +57043,7 @@
         <v>13.29</v>
       </c>
       <c r="L178" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M178" s="4" t="n">
         <v>2</v>
@@ -57129,7 +57129,7 @@
         <v>13.27</v>
       </c>
       <c r="L179" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M179" s="4" t="n">
         <v>2</v>
@@ -57215,7 +57215,7 @@
         <v>13.16</v>
       </c>
       <c r="L180" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M180" s="4" t="n">
         <v>2</v>
@@ -57301,7 +57301,7 @@
         <v>13.14</v>
       </c>
       <c r="L181" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M181" s="4" t="n">
         <v>2</v>
@@ -57387,7 +57387,7 @@
         <v>13.06</v>
       </c>
       <c r="L182" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M182" s="4" t="n">
         <v>2</v>
@@ -57473,7 +57473,7 @@
         <v>13.05</v>
       </c>
       <c r="L183" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M183" s="4" t="n">
         <v>2</v>
@@ -57559,7 +57559,7 @@
         <v>13.04</v>
       </c>
       <c r="L184" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M184" s="4" t="n">
         <v>2</v>
@@ -57645,7 +57645,7 @@
         <v>12.99</v>
       </c>
       <c r="L185" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M185" s="4" t="n">
         <v>2</v>
@@ -57731,7 +57731,7 @@
         <v>12.98</v>
       </c>
       <c r="L186" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M186" s="4" t="n">
         <v>2</v>
@@ -57817,7 +57817,7 @@
         <v>12.95</v>
       </c>
       <c r="L187" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M187" s="4" t="n">
         <v>2</v>
@@ -57903,7 +57903,7 @@
         <v>12.92</v>
       </c>
       <c r="L188" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M188" s="4" t="n">
         <v>2</v>
@@ -57989,7 +57989,7 @@
         <v>12.84</v>
       </c>
       <c r="L189" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M189" s="4" t="n">
         <v>2</v>
@@ -58075,7 +58075,7 @@
         <v>12.76</v>
       </c>
       <c r="L190" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M190" s="4" t="n">
         <v>2</v>
@@ -58161,7 +58161,7 @@
         <v>12.72</v>
       </c>
       <c r="L191" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M191" s="4" t="n">
         <v>2</v>
@@ -58247,7 +58247,7 @@
         <v>12.71</v>
       </c>
       <c r="L192" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M192" s="4" t="n">
         <v>2</v>
@@ -58333,7 +58333,7 @@
         <v>12.56</v>
       </c>
       <c r="L193" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M193" s="4" t="n">
         <v>2</v>
@@ -58419,7 +58419,7 @@
         <v>12.56</v>
       </c>
       <c r="L194" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M194" s="4" t="n">
         <v>2</v>
@@ -58505,7 +58505,7 @@
         <v>12.51</v>
       </c>
       <c r="L195" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M195" s="4" t="n">
         <v>2</v>
@@ -58591,7 +58591,7 @@
         <v>12.5</v>
       </c>
       <c r="L196" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M196" s="4" t="n">
         <v>2</v>
@@ -58677,7 +58677,7 @@
         <v>12.34</v>
       </c>
       <c r="L197" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M197" s="4" t="n">
         <v>2</v>
@@ -58763,7 +58763,7 @@
         <v>12.32</v>
       </c>
       <c r="L198" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M198" s="4" t="n">
         <v>2</v>
@@ -58849,7 +58849,7 @@
         <v>12.32</v>
       </c>
       <c r="L199" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M199" s="4" t="n">
         <v>2</v>
@@ -58935,7 +58935,7 @@
         <v>12.28</v>
       </c>
       <c r="L200" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M200" s="4" t="n">
         <v>2</v>
@@ -59021,7 +59021,7 @@
         <v>12.22</v>
       </c>
       <c r="L201" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M201" s="4" t="n">
         <v>2</v>
@@ -59107,7 +59107,7 @@
         <v>12.21</v>
       </c>
       <c r="L202" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M202" s="4" t="n">
         <v>2</v>
@@ -59193,7 +59193,7 @@
         <v>12.08</v>
       </c>
       <c r="L203" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M203" s="4" t="n">
         <v>2</v>
@@ -59279,7 +59279,7 @@
         <v>12.05</v>
       </c>
       <c r="L204" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M204" s="4" t="n">
         <v>2</v>
@@ -59365,7 +59365,7 @@
         <v>11.92</v>
       </c>
       <c r="L205" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M205" s="4" t="n">
         <v>2</v>
@@ -59451,7 +59451,7 @@
         <v>11.91</v>
       </c>
       <c r="L206" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M206" s="4" t="n">
         <v>2</v>
@@ -59537,7 +59537,7 @@
         <v>11.88</v>
       </c>
       <c r="L207" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M207" s="4" t="n">
         <v>2</v>
@@ -59623,7 +59623,7 @@
         <v>11.85</v>
       </c>
       <c r="L208" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M208" s="4" t="n">
         <v>2</v>
@@ -59709,7 +59709,7 @@
         <v>11.79</v>
       </c>
       <c r="L209" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M209" s="4" t="n">
         <v>1</v>
@@ -59795,7 +59795,7 @@
         <v>11.76</v>
       </c>
       <c r="L210" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M210" s="4" t="n">
         <v>1</v>
@@ -59881,7 +59881,7 @@
         <v>11.75</v>
       </c>
       <c r="L211" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M211" s="4" t="n">
         <v>1</v>
@@ -59967,7 +59967,7 @@
         <v>11.73</v>
       </c>
       <c r="L212" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M212" s="4" t="n">
         <v>1</v>
@@ -60053,7 +60053,7 @@
         <v>11.7</v>
       </c>
       <c r="L213" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M213" s="4" t="n">
         <v>1</v>
@@ -60139,7 +60139,7 @@
         <v>11.6</v>
       </c>
       <c r="L214" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M214" s="4" t="n">
         <v>1</v>
@@ -60225,7 +60225,7 @@
         <v>11.57</v>
       </c>
       <c r="L215" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M215" s="4" t="n">
         <v>1</v>
@@ -60311,7 +60311,7 @@
         <v>11.54</v>
       </c>
       <c r="L216" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M216" s="4" t="n">
         <v>1</v>
@@ -60397,7 +60397,7 @@
         <v>11.53</v>
       </c>
       <c r="L217" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M217" s="4" t="n">
         <v>1</v>
@@ -60483,7 +60483,7 @@
         <v>11.53</v>
       </c>
       <c r="L218" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M218" s="4" t="n">
         <v>1</v>
@@ -60569,7 +60569,7 @@
         <v>11.51</v>
       </c>
       <c r="L219" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M219" s="4" t="n">
         <v>1</v>
@@ -60655,7 +60655,7 @@
         <v>11.37</v>
       </c>
       <c r="L220" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M220" s="4" t="n">
         <v>1</v>
@@ -60741,7 +60741,7 @@
         <v>11.22</v>
       </c>
       <c r="L221" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M221" s="4" t="n">
         <v>1</v>
@@ -60827,7 +60827,7 @@
         <v>11.07</v>
       </c>
       <c r="L222" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M222" s="4" t="n">
         <v>1</v>
@@ -60913,7 +60913,7 @@
         <v>11</v>
       </c>
       <c r="L223" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M223" s="4" t="n">
         <v>1</v>
@@ -60999,7 +60999,7 @@
         <v>10.92</v>
       </c>
       <c r="L224" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M224" s="4" t="n">
         <v>1</v>
@@ -61085,7 +61085,7 @@
         <v>10.89</v>
       </c>
       <c r="L225" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M225" s="4" t="n">
         <v>1</v>
@@ -61171,7 +61171,7 @@
         <v>10.83</v>
       </c>
       <c r="L226" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M226" s="4" t="n">
         <v>1</v>
@@ -61257,7 +61257,7 @@
         <v>10.81</v>
       </c>
       <c r="L227" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M227" s="4" t="n">
         <v>1</v>
@@ -61343,7 +61343,7 @@
         <v>10.74</v>
       </c>
       <c r="L228" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M228" s="4" t="n">
         <v>1</v>
@@ -61429,7 +61429,7 @@
         <v>10.7</v>
       </c>
       <c r="L229" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M229" s="4" t="n">
         <v>1</v>
@@ -61515,7 +61515,7 @@
         <v>10.59</v>
       </c>
       <c r="L230" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M230" s="4" t="n">
         <v>1</v>
@@ -61601,7 +61601,7 @@
         <v>10.59</v>
       </c>
       <c r="L231" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M231" s="4" t="n">
         <v>1</v>
@@ -61687,7 +61687,7 @@
         <v>10.5</v>
       </c>
       <c r="L232" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M232" s="4" t="n">
         <v>1</v>
@@ -61773,7 +61773,7 @@
         <v>10.48</v>
       </c>
       <c r="L233" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M233" s="4" t="n">
         <v>1</v>
@@ -61859,7 +61859,7 @@
         <v>10.45</v>
       </c>
       <c r="L234" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M234" s="4" t="n">
         <v>1</v>
@@ -61945,7 +61945,7 @@
         <v>10.44</v>
       </c>
       <c r="L235" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M235" s="4" t="n">
         <v>1</v>
@@ -62031,7 +62031,7 @@
         <v>10.42</v>
       </c>
       <c r="L236" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M236" s="4" t="n">
         <v>1</v>
@@ -62117,7 +62117,7 @@
         <v>10.31</v>
       </c>
       <c r="L237" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M237" s="4" t="n">
         <v>1</v>
@@ -62203,7 +62203,7 @@
         <v>10.3</v>
       </c>
       <c r="L238" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M238" s="4" t="n">
         <v>1</v>
@@ -62289,7 +62289,7 @@
         <v>10.24</v>
       </c>
       <c r="L239" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M239" s="4" t="n">
         <v>1</v>
@@ -62375,7 +62375,7 @@
         <v>10.23</v>
       </c>
       <c r="L240" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M240" s="4" t="n">
         <v>1</v>
@@ -62461,7 +62461,7 @@
         <v>10.14</v>
       </c>
       <c r="L241" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M241" s="4" t="n">
         <v>1</v>
@@ -62547,7 +62547,7 @@
         <v>10.11</v>
       </c>
       <c r="L242" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M242" s="4" t="n">
         <v>1</v>
@@ -62633,7 +62633,7 @@
         <v>10.09</v>
       </c>
       <c r="L243" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M243" s="4" t="n">
         <v>1</v>
@@ -62719,7 +62719,7 @@
         <v>10.01</v>
       </c>
       <c r="L244" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M244" s="4" t="n">
         <v>1</v>
@@ -62805,7 +62805,7 @@
         <v>9.99</v>
       </c>
       <c r="L245" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M245" s="4" t="n">
         <v>1</v>
@@ -62891,7 +62891,7 @@
         <v>9.98</v>
       </c>
       <c r="L246" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M246" s="4" t="n">
         <v>1</v>
@@ -62977,7 +62977,7 @@
         <v>9.869999999999999</v>
       </c>
       <c r="L247" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M247" s="4" t="n">
         <v>1</v>
@@ -63063,7 +63063,7 @@
         <v>9.83</v>
       </c>
       <c r="L248" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M248" s="4" t="n">
         <v>1</v>
@@ -63149,7 +63149,7 @@
         <v>9.75</v>
       </c>
       <c r="L249" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M249" s="4" t="n">
         <v>1</v>
@@ -63235,7 +63235,7 @@
         <v>9.74</v>
       </c>
       <c r="L250" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M250" s="4" t="n">
         <v>1</v>
@@ -63321,7 +63321,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="L251" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M251" s="4" t="n">
         <v>1</v>
@@ -63407,7 +63407,7 @@
         <v>9.69</v>
       </c>
       <c r="L252" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M252" s="4" t="n">
         <v>1</v>
@@ -63493,7 +63493,7 @@
         <v>9.550000000000001</v>
       </c>
       <c r="L253" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M253" s="4" t="n">
         <v>1</v>
@@ -63579,7 +63579,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="L254" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M254" s="4" t="n">
         <v>1</v>
@@ -63665,7 +63665,7 @@
         <v>9.52</v>
       </c>
       <c r="L255" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M255" s="4" t="n">
         <v>1</v>
@@ -63751,7 +63751,7 @@
         <v>9.5</v>
       </c>
       <c r="L256" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M256" s="4" t="n">
         <v>1</v>
@@ -63837,7 +63837,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="L257" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M257" s="4" t="n">
         <v>1</v>
@@ -63923,7 +63923,7 @@
         <v>9.44</v>
       </c>
       <c r="L258" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M258" s="4" t="n">
         <v>1</v>
@@ -64009,7 +64009,7 @@
         <v>9.41</v>
       </c>
       <c r="L259" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M259" s="4" t="n">
         <v>1</v>
@@ -64095,7 +64095,7 @@
         <v>9.4</v>
       </c>
       <c r="L260" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M260" s="4" t="n">
         <v>1</v>
@@ -64181,7 +64181,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="L261" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M261" s="4" t="n">
         <v>1</v>
@@ -64267,7 +64267,7 @@
         <v>9.16</v>
       </c>
       <c r="L262" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M262" s="4" t="n">
         <v>1</v>
@@ -64353,7 +64353,7 @@
         <v>9.16</v>
       </c>
       <c r="L263" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M263" s="4" t="n">
         <v>1</v>
@@ -64439,7 +64439,7 @@
         <v>9.050000000000001</v>
       </c>
       <c r="L264" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M264" s="4" t="n">
         <v>1</v>
@@ -64525,7 +64525,7 @@
         <v>9.029999999999999</v>
       </c>
       <c r="L265" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M265" s="4" t="n">
         <v>1</v>
@@ -64611,7 +64611,7 @@
         <v>9.029999999999999</v>
       </c>
       <c r="L266" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M266" s="4" t="n">
         <v>1</v>
@@ -64697,7 +64697,7 @@
         <v>9.029999999999999</v>
       </c>
       <c r="L267" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M267" s="4" t="n">
         <v>1</v>
@@ -64783,7 +64783,7 @@
         <v>9</v>
       </c>
       <c r="L268" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M268" s="4" t="n">
         <v>1</v>
@@ -64869,7 +64869,7 @@
         <v>9</v>
       </c>
       <c r="L269" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M269" s="4" t="n">
         <v>1</v>
@@ -64955,7 +64955,7 @@
         <v>8.970000000000001</v>
       </c>
       <c r="L270" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M270" s="4" t="n">
         <v>1</v>
@@ -65041,7 +65041,7 @@
         <v>8.859999999999999</v>
       </c>
       <c r="L271" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M271" s="4" t="n">
         <v>1</v>
@@ -65127,7 +65127,7 @@
         <v>8.76</v>
       </c>
       <c r="L272" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M272" s="4" t="n">
         <v>1</v>
@@ -65213,7 +65213,7 @@
         <v>8.74</v>
       </c>
       <c r="L273" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M273" s="4" t="n">
         <v>1</v>
@@ -65299,7 +65299,7 @@
         <v>8.65</v>
       </c>
       <c r="L274" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M274" s="4" t="n">
         <v>1</v>
@@ -65385,7 +65385,7 @@
         <v>8.6</v>
       </c>
       <c r="L275" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M275" s="4" t="n">
         <v>1</v>
@@ -65471,7 +65471,7 @@
         <v>8.6</v>
       </c>
       <c r="L276" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M276" s="4" t="n">
         <v>1</v>
@@ -65557,7 +65557,7 @@
         <v>8.48</v>
       </c>
       <c r="L277" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M277" s="4" t="n">
         <v>1</v>
@@ -65643,7 +65643,7 @@
         <v>8.460000000000001</v>
       </c>
       <c r="L278" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M278" s="4" t="n">
         <v>1</v>
@@ -65729,7 +65729,7 @@
         <v>8.43</v>
       </c>
       <c r="L279" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M279" s="4" t="n">
         <v>1</v>
@@ -65815,7 +65815,7 @@
         <v>8.42</v>
       </c>
       <c r="L280" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M280" s="4" t="n">
         <v>1</v>
@@ -65901,7 +65901,7 @@
         <v>8.4</v>
       </c>
       <c r="L281" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M281" s="4" t="n">
         <v>1</v>
@@ -65987,7 +65987,7 @@
         <v>8.390000000000001</v>
       </c>
       <c r="L282" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M282" s="4" t="n">
         <v>1</v>
@@ -66073,7 +66073,7 @@
         <v>8.359999999999999</v>
       </c>
       <c r="L283" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M283" s="4" t="n">
         <v>1</v>
@@ -66159,7 +66159,7 @@
         <v>8.359999999999999</v>
       </c>
       <c r="L284" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M284" s="4" t="n">
         <v>1</v>
@@ -66245,7 +66245,7 @@
         <v>8.33</v>
       </c>
       <c r="L285" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M285" s="4" t="n">
         <v>1</v>
@@ -66331,7 +66331,7 @@
         <v>8.26</v>
       </c>
       <c r="L286" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M286" s="4" t="n">
         <v>1</v>
@@ -66417,7 +66417,7 @@
         <v>8.220000000000001</v>
       </c>
       <c r="L287" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M287" s="4" t="n">
         <v>1</v>
@@ -66503,7 +66503,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="L288" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M288" s="4" t="n">
         <v>1</v>
@@ -66589,7 +66589,7 @@
         <v>8.01</v>
       </c>
       <c r="L289" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M289" s="4" t="n">
         <v>1</v>
@@ -66675,7 +66675,7 @@
         <v>7.97</v>
       </c>
       <c r="L290" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M290" s="4" t="n">
         <v>1</v>
@@ -66761,7 +66761,7 @@
         <v>7.94</v>
       </c>
       <c r="L291" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M291" s="4" t="n">
         <v>1</v>
@@ -66847,7 +66847,7 @@
         <v>7.89</v>
       </c>
       <c r="L292" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M292" s="4" t="n">
         <v>1</v>
@@ -66933,7 +66933,7 @@
         <v>7.83</v>
       </c>
       <c r="L293" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M293" s="4" t="n">
         <v>1</v>
@@ -67019,7 +67019,7 @@
         <v>7.78</v>
       </c>
       <c r="L294" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M294" s="4" t="n">
         <v>1</v>
@@ -67105,7 +67105,7 @@
         <v>7.71</v>
       </c>
       <c r="L295" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M295" s="4" t="n">
         <v>1</v>
@@ -67191,7 +67191,7 @@
         <v>7.7</v>
       </c>
       <c r="L296" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M296" s="4" t="n">
         <v>1</v>
@@ -67277,7 +67277,7 @@
         <v>7.69</v>
       </c>
       <c r="L297" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M297" s="4" t="n">
         <v>1</v>
@@ -67363,7 +67363,7 @@
         <v>7.68</v>
       </c>
       <c r="L298" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M298" s="4" t="n">
         <v>1</v>
@@ -67449,7 +67449,7 @@
         <v>7.67</v>
       </c>
       <c r="L299" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M299" s="4" t="n">
         <v>1</v>
@@ -67535,7 +67535,7 @@
         <v>7.67</v>
       </c>
       <c r="L300" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M300" s="4" t="n">
         <v>1</v>
@@ -67621,7 +67621,7 @@
         <v>7.62</v>
       </c>
       <c r="L301" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M301" s="4" t="n">
         <v>1</v>
@@ -67707,7 +67707,7 @@
         <v>7.59</v>
       </c>
       <c r="L302" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M302" s="4" t="n">
         <v>0</v>
@@ -67793,7 +67793,7 @@
         <v>7.56</v>
       </c>
       <c r="L303" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M303" s="4" t="n">
         <v>0</v>
@@ -67879,7 +67879,7 @@
         <v>7.52</v>
       </c>
       <c r="L304" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M304" s="4" t="n">
         <v>0</v>
@@ -67965,7 +67965,7 @@
         <v>7.52</v>
       </c>
       <c r="L305" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M305" s="4" t="n">
         <v>0</v>
@@ -68051,7 +68051,7 @@
         <v>7.48</v>
       </c>
       <c r="L306" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M306" s="4" t="n">
         <v>0</v>
@@ -68137,7 +68137,7 @@
         <v>7.48</v>
       </c>
       <c r="L307" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M307" s="4" t="n">
         <v>0</v>
@@ -68223,7 +68223,7 @@
         <v>7.45</v>
       </c>
       <c r="L308" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M308" s="4" t="n">
         <v>0</v>
@@ -68309,7 +68309,7 @@
         <v>7.39</v>
       </c>
       <c r="L309" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M309" s="4" t="n">
         <v>0</v>
@@ -68395,7 +68395,7 @@
         <v>7.37</v>
       </c>
       <c r="L310" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M310" s="4" t="n">
         <v>0</v>
@@ -68481,7 +68481,7 @@
         <v>7.35</v>
       </c>
       <c r="L311" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M311" s="4" t="n">
         <v>0</v>
@@ -68567,7 +68567,7 @@
         <v>7.31</v>
       </c>
       <c r="L312" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M312" s="4" t="n">
         <v>0</v>
@@ -68653,7 +68653,7 @@
         <v>7.23</v>
       </c>
       <c r="L313" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M313" s="4" t="n">
         <v>0</v>
@@ -68739,7 +68739,7 @@
         <v>7.15</v>
       </c>
       <c r="L314" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M314" s="4" t="n">
         <v>0</v>
@@ -68825,7 +68825,7 @@
         <v>7.1</v>
       </c>
       <c r="L315" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M315" s="4" t="n">
         <v>0</v>
@@ -68911,7 +68911,7 @@
         <v>6.96</v>
       </c>
       <c r="L316" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M316" s="4" t="n">
         <v>0</v>
@@ -68997,7 +68997,7 @@
         <v>6.93</v>
       </c>
       <c r="L317" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M317" s="4" t="n">
         <v>0</v>
@@ -69083,7 +69083,7 @@
         <v>6.91</v>
       </c>
       <c r="L318" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M318" s="4" t="n">
         <v>0</v>
@@ -69169,7 +69169,7 @@
         <v>6.79</v>
       </c>
       <c r="L319" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M319" s="4" t="n">
         <v>0</v>
@@ -69255,7 +69255,7 @@
         <v>6.78</v>
       </c>
       <c r="L320" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M320" s="4" t="n">
         <v>0</v>
@@ -69341,7 +69341,7 @@
         <v>6.77</v>
       </c>
       <c r="L321" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M321" s="4" t="n">
         <v>0</v>
@@ -69427,7 +69427,7 @@
         <v>6.75</v>
       </c>
       <c r="L322" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M322" s="4" t="n">
         <v>0</v>
@@ -69513,7 +69513,7 @@
         <v>6.66</v>
       </c>
       <c r="L323" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M323" s="4" t="n">
         <v>0</v>
@@ -69599,7 +69599,7 @@
         <v>6.66</v>
       </c>
       <c r="L324" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M324" s="4" t="n">
         <v>0</v>
@@ -69685,7 +69685,7 @@
         <v>6.62</v>
       </c>
       <c r="L325" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M325" s="4" t="n">
         <v>0</v>
@@ -69771,7 +69771,7 @@
         <v>6.61</v>
       </c>
       <c r="L326" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M326" s="4" t="n">
         <v>0</v>
@@ -69857,7 +69857,7 @@
         <v>6.61</v>
       </c>
       <c r="L327" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M327" s="4" t="n">
         <v>0</v>
@@ -69943,7 +69943,7 @@
         <v>6.56</v>
       </c>
       <c r="L328" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M328" s="4" t="n">
         <v>0</v>
@@ -70029,7 +70029,7 @@
         <v>6.49</v>
       </c>
       <c r="L329" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M329" s="4" t="n">
         <v>0</v>
@@ -70115,7 +70115,7 @@
         <v>6.43</v>
       </c>
       <c r="L330" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M330" s="4" t="n">
         <v>0</v>
@@ -70201,7 +70201,7 @@
         <v>6.28</v>
       </c>
       <c r="L331" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M331" s="4" t="n">
         <v>0</v>
@@ -70287,7 +70287,7 @@
         <v>6.22</v>
       </c>
       <c r="L332" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M332" s="4" t="n">
         <v>0</v>
@@ -70373,7 +70373,7 @@
         <v>6.15</v>
       </c>
       <c r="L333" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M333" s="4" t="n">
         <v>0</v>
@@ -70459,7 +70459,7 @@
         <v>6.05</v>
       </c>
       <c r="L334" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M334" s="4" t="n">
         <v>0</v>
@@ -70545,7 +70545,7 @@
         <v>5.87</v>
       </c>
       <c r="L335" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M335" s="4" t="n">
         <v>0</v>
@@ -70631,7 +70631,7 @@
         <v>5.84</v>
       </c>
       <c r="L336" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M336" s="4" t="n">
         <v>0</v>
@@ -70717,7 +70717,7 @@
         <v>5.78</v>
       </c>
       <c r="L337" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M337" s="4" t="n">
         <v>0</v>
@@ -70803,7 +70803,7 @@
         <v>5.61</v>
       </c>
       <c r="L338" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M338" s="4" t="n">
         <v>0</v>
@@ -70889,7 +70889,7 @@
         <v>5.59</v>
       </c>
       <c r="L339" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M339" s="4" t="n">
         <v>0</v>
@@ -70975,7 +70975,7 @@
         <v>5.58</v>
       </c>
       <c r="L340" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M340" s="4" t="n">
         <v>0</v>
@@ -71061,7 +71061,7 @@
         <v>5.56</v>
       </c>
       <c r="L341" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M341" s="4" t="n">
         <v>0</v>
@@ -71147,7 +71147,7 @@
         <v>5.51</v>
       </c>
       <c r="L342" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M342" s="4" t="n">
         <v>0</v>
@@ -71233,7 +71233,7 @@
         <v>5.45</v>
       </c>
       <c r="L343" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M343" s="4" t="n">
         <v>0</v>
@@ -71319,7 +71319,7 @@
         <v>5.4</v>
       </c>
       <c r="L344" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M344" s="4" t="n">
         <v>0</v>
@@ -71405,7 +71405,7 @@
         <v>5.39</v>
       </c>
       <c r="L345" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M345" s="4" t="n">
         <v>0</v>
@@ -71491,7 +71491,7 @@
         <v>5.36</v>
       </c>
       <c r="L346" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M346" s="4" t="n">
         <v>0</v>
@@ -71577,7 +71577,7 @@
         <v>5.33</v>
       </c>
       <c r="L347" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M347" s="4" t="n">
         <v>0</v>
@@ -71663,7 +71663,7 @@
         <v>5.13</v>
       </c>
       <c r="L348" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M348" s="4" t="n">
         <v>0</v>
@@ -71749,7 +71749,7 @@
         <v>5.11</v>
       </c>
       <c r="L349" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M349" s="4" t="n">
         <v>0</v>
@@ -71835,7 +71835,7 @@
         <v>5.09</v>
       </c>
       <c r="L350" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M350" s="4" t="n">
         <v>0</v>
@@ -71921,7 +71921,7 @@
         <v>5.04</v>
       </c>
       <c r="L351" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M351" s="4" t="n">
         <v>0</v>
@@ -72007,7 +72007,7 @@
         <v>5.03</v>
       </c>
       <c r="L352" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M352" s="4" t="n">
         <v>0</v>
@@ -72093,7 +72093,7 @@
         <v>4.98</v>
       </c>
       <c r="L353" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M353" s="4" t="n">
         <v>0</v>
@@ -72179,7 +72179,7 @@
         <v>4.87</v>
       </c>
       <c r="L354" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M354" s="4" t="n">
         <v>0</v>
@@ -72265,7 +72265,7 @@
         <v>4.74</v>
       </c>
       <c r="L355" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M355" s="4" t="n">
         <v>0</v>
@@ -72351,7 +72351,7 @@
         <v>4.74</v>
       </c>
       <c r="L356" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M356" s="4" t="n">
         <v>0</v>
@@ -72437,7 +72437,7 @@
         <v>4.73</v>
       </c>
       <c r="L357" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M357" s="4" t="n">
         <v>0</v>
@@ -72523,7 +72523,7 @@
         <v>4.64</v>
       </c>
       <c r="L358" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M358" s="4" t="n">
         <v>0</v>
@@ -72609,7 +72609,7 @@
         <v>4.6</v>
       </c>
       <c r="L359" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M359" s="4" t="n">
         <v>0</v>
@@ -72695,7 +72695,7 @@
         <v>4.6</v>
       </c>
       <c r="L360" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M360" s="4" t="n">
         <v>0</v>
@@ -72781,7 +72781,7 @@
         <v>4.57</v>
       </c>
       <c r="L361" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M361" s="4" t="n">
         <v>0</v>
@@ -72867,7 +72867,7 @@
         <v>4.54</v>
       </c>
       <c r="L362" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M362" s="4" t="n">
         <v>0</v>
@@ -72953,7 +72953,7 @@
         <v>4.46</v>
       </c>
       <c r="L363" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M363" s="4" t="n">
         <v>0</v>
@@ -73039,7 +73039,7 @@
         <v>4.46</v>
       </c>
       <c r="L364" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M364" s="4" t="n">
         <v>0</v>
@@ -73125,7 +73125,7 @@
         <v>4.42</v>
       </c>
       <c r="L365" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M365" s="4" t="n">
         <v>0</v>
@@ -73211,7 +73211,7 @@
         <v>4.31</v>
       </c>
       <c r="L366" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M366" s="4" t="n">
         <v>0</v>
@@ -73297,7 +73297,7 @@
         <v>4.24</v>
       </c>
       <c r="L367" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M367" s="4" t="n">
         <v>0</v>
@@ -73383,7 +73383,7 @@
         <v>4.2</v>
       </c>
       <c r="L368" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M368" s="4" t="n">
         <v>0</v>
@@ -73469,7 +73469,7 @@
         <v>4.12</v>
       </c>
       <c r="L369" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M369" s="4" t="n">
         <v>0</v>
@@ -73555,7 +73555,7 @@
         <v>4.08</v>
       </c>
       <c r="L370" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M370" s="4" t="n">
         <v>0</v>
@@ -73641,7 +73641,7 @@
         <v>4.05</v>
       </c>
       <c r="L371" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M371" s="4" t="n">
         <v>0</v>
@@ -73727,7 +73727,7 @@
         <v>3.96</v>
       </c>
       <c r="L372" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M372" s="4" t="n">
         <v>0</v>
@@ -73813,7 +73813,7 @@
         <v>3.8</v>
       </c>
       <c r="L373" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M373" s="4" t="n">
         <v>0</v>
@@ -73899,7 +73899,7 @@
         <v>3.73</v>
       </c>
       <c r="L374" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M374" s="4" t="n">
         <v>0</v>
@@ -73985,7 +73985,7 @@
         <v>3.7</v>
       </c>
       <c r="L375" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M375" s="4" t="n">
         <v>0</v>
@@ -74071,7 +74071,7 @@
         <v>3.61</v>
       </c>
       <c r="L376" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M376" s="4" t="n">
         <v>0</v>
@@ -74157,7 +74157,7 @@
         <v>3.53</v>
       </c>
       <c r="L377" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M377" s="4" t="n">
         <v>0</v>
@@ -74243,7 +74243,7 @@
         <v>3.44</v>
       </c>
       <c r="L378" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M378" s="4" t="n">
         <v>0</v>
@@ -74329,7 +74329,7 @@
         <v>3.4</v>
       </c>
       <c r="L379" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M379" s="4" t="n">
         <v>0</v>
@@ -74415,7 +74415,7 @@
         <v>3.31</v>
       </c>
       <c r="L380" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M380" s="4" t="n">
         <v>0</v>
@@ -74501,7 +74501,7 @@
         <v>3.15</v>
       </c>
       <c r="L381" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M381" s="4" t="n">
         <v>0</v>
@@ -74587,7 +74587,7 @@
         <v>3.01</v>
       </c>
       <c r="L382" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M382" s="4" t="n">
         <v>0</v>
